--- a/feedback_forms/004_dreams_delivery_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/004_dreams_delivery_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>product_condition</t>
+          <t>product_condition_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>delivery_time</t>
+          <t>delivery_time_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What was the delivery time?</t>
+          <t>Delivery Time 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>order_date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>order_time</t>
+          <t>order_time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>order_number</t>
+          <t>order_number_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is your order number?</t>
+          <t>Order Number 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>product_name_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What is your product name?</t>
+          <t>Product Name 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
